--- a/runs/RELX/2026-10-14/bear/scratch/g_exit_wkl/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_exit_wkl/out/dcf.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1545919344753032</v>
+        <v>0.1340797166838067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.054629</v>
+        <v>0.043808</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2044.926705519653</v>
+        <v>2102.881781249673</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11133.7332424089</v>
+        <v>11302.6880463898</v>
       </c>
     </row>
     <row r="21">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2207.684566536077</v>
+        <v>2422.97168356811</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>53350.70918097567</v>
+        <v>53350.55432246983</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>35316.33095416009</v>
+        <v>36317.12235706395</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46450.06419656899</v>
+        <v>47619.81040345375</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>39453.06419656899</v>
+        <v>40622.81040345375</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>39334.28893737948</v>
+        <v>40354.84093624028</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>22.55723716663478</v>
+        <v>23.14249837514005</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2255.723716663478</v>
+        <v>2314.249837514005</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.1859531878</v>
+        <v>-0.1648322492</v>
       </c>
     </row>
   </sheetData>
